--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 01:58</t>
+          <t>更新时间: 2026-08-04 02:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 02:11</t>
+          <t>更新时间: 2026-08-04 02:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 02:25</t>
+          <t>更新时间: 2026-08-04 02:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 02:44</t>
+          <t>更新时间: 2026-08-04 02:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 02:46</t>
+          <t>更新时间: 2026-08-04 02:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 02:50</t>
+          <t>更新时间: 2026-08-04 18:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 18:02</t>
+          <t>更新时间: 2026-08-04 18:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 19:00</t>
+          <t>更新时间: 2026-08-04 19:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 19:12</t>
+          <t>更新时间: 2026-08-04 19:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-04 19:49</t>
+          <t>更新时间: 2026-08-05 16:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 16:24</t>
+          <t>更新时间: 2026-08-05 18:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 18:14</t>
+          <t>更新时间: 2026-08-05 18:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-05 18:17</t>
+          <t>更新时间: 2026-08-05 19:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 16:20</t>
+          <t>更新时间: 2026-08-06 18:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 18:17</t>
+          <t>更新时间: 2026-08-06 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-06 18:49</t>
+          <t>更新时间: 2026-08-06 19:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-07 16:20</t>
+          <t>更新时间: 2026-08-08 12:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 12:09</t>
+          <t>更新时间: 2026-08-08 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 12:37</t>
+          <t>更新时间: 2026-08-08 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 13:12</t>
+          <t>更新时间: 2026-08-08 14:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-08 14:05</t>
+          <t>更新时间: 2026-08-09 12:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 12:19</t>
+          <t>更新时间: 2026-08-09 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 13:31</t>
+          <t>更新时间: 2026-08-09 14:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-09 14:10</t>
+          <t>更新时间: 2026-08-10 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-10 17:01</t>
+          <t>更新时间: 2026-08-11 12:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 15:59</t>
+          <t>更新时间: 2026-08-12 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 13:31</t>
+          <t>更新时间: 2026-08-12 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 16:48</t>
+          <t>更新时间: 2026-08-13 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-13 16:52</t>
+          <t>更新时间: 2026-08-14 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 13:37</t>
+          <t>更新时间: 2026-08-14 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 08:13</t>
+          <t>更新时间: 2026-08-15 11:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 11:08</t>
+          <t>更新时间: 2026-08-15 11:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 13:53</t>
+          <t>更新时间: 2026-08-18 08:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 08:16</t>
+          <t>更新时间: 2026-08-18 11:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 13:16</t>
+          <t>更新时间: 2026-08-19 08:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 08:17</t>
+          <t>更新时间: 2026-08-19 11:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 11:15</t>
+          <t>更新时间: 2026-08-19 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 11:32</t>
+          <t>更新时间: 2026-08-19 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 12:21</t>
+          <t>更新时间: 2026-08-19 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 13:16</t>
+          <t>更新时间: 2026-08-20 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 08:13</t>
+          <t>更新时间: 2026-08-20 11:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 11:33</t>
+          <t>更新时间: 2026-08-20 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 12:21</t>
+          <t>更新时间: 2026-08-20 13:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 13:19</t>
+          <t>更新时间: 2026-08-21 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 08:14</t>
+          <t>更新时间: 2026-08-21 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 13:49</t>
+          <t>更新时间: 2026-08-22 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 08:14</t>
+          <t>更新时间: 2026-08-22 11:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 11:25</t>
+          <t>更新时间: 2026-08-22 12:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 12:09</t>
+          <t>更新时间: 2026-08-22 13:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 13:04</t>
+          <t>更新时间: 2026-08-23 08:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 08:16</t>
+          <t>更新时间: 2026-08-23 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 11:32</t>
+          <t>更新时间: 2026-08-23 11:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 13:16</t>
+          <t>更新时间: 2026-08-24 08:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 08:10</t>
+          <t>更新时间: 2026-08-24 11:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 11:36</t>
+          <t>更新时间: 2026-08-24 12:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 12:03</t>
+          <t>更新时间: 2026-08-24 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 12:32</t>
+          <t>更新时间: 2026-08-24 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 13:58</t>
+          <t>更新时间: 2026-08-25 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 08:13</t>
+          <t>更新时间: 2026-08-25 11:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 13:49</t>
+          <t>更新时间: 2026-08-26 08:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 08:18</t>
+          <t>更新时间: 2026-08-26 11:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 11:38</t>
+          <t>更新时间: 2026-08-26 12:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 13:53</t>
+          <t>更新时间: 2026-08-28 14:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 14:25</t>
+          <t>更新时间: 2026-08-28 14:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 05:26</t>
+          <t>更新时间: 2026-08-29 07:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 07:33</t>
+          <t>更新时间: 2026-08-29 08:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 08:19</t>
+          <t>更新时间: 2026-08-29 09:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 09:03</t>
+          <t>更新时间: 2026-08-29 10:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 10:26</t>
+          <t>更新时间: 2026-08-29 12:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 12:04</t>
+          <t>更新时间: 2026-08-30 07:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 07:44</t>
+          <t>更新时间: 2026-08-30 08:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 08:19</t>
+          <t>更新时间: 2026-08-30 09:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 09:03</t>
+          <t>更新时间: 2026-08-30 10:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 10:26</t>
+          <t>更新时间: 2026-08-30 12:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 12:04</t>
+          <t>更新时间: 2026-08-31 07:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 07:44</t>
+          <t>更新时间: 2026-08-31 08:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 08:19</t>
+          <t>更新时间: 2026-08-31 09:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 09:03</t>
+          <t>更新时间: 2026-08-31 10:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 10:26</t>
+          <t>更新时间: 2026-08-31 12:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 12:04</t>
+          <t>更新时间: 2026-09-01 07:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 07:45</t>
+          <t>更新时间: 2026-09-01 08:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 08:36</t>
+          <t>更新时间: 2026-09-01 09:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 09:06</t>
+          <t>更新时间: 2026-09-01 10:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 10:30</t>
+          <t>更新时间: 2026-09-01 12:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 12:08</t>
+          <t>更新时间: 2026-09-02 07:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 07:44</t>
+          <t>更新时间: 2026-09-02 08:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 08:33</t>
+          <t>更新时间: 2026-09-02 09:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 09:05</t>
+          <t>更新时间: 2026-09-02 10:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 10:42</t>
+          <t>更新时间: 2026-09-02 12:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 12:08</t>
+          <t>更新时间: 2026-09-03 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 07:49</t>
+          <t>更新时间: 2026-09-03 08:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 08:35</t>
+          <t>更新时间: 2026-09-03 09:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 09:06</t>
+          <t>更新时间: 2026-09-03 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:12</t>
+          <t>更新时间: 2026-09-03 13:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:33</t>
+          <t>更新时间: 2026-09-04 09:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 09:20</t>
+          <t>更新时间: 2026-09-04 12:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 12:31</t>
+          <t>更新时间: 2026-09-04 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:21</t>
+          <t>更新时间: 2026-09-04 15:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 15:17</t>
+          <t>更新时间: 2026-09-04 16:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 16:26</t>
+          <t>更新时间: 2026-09-05 09:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 09:26</t>
+          <t>更新时间: 2026-09-05 12:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 12:26</t>
+          <t>更新时间: 2026-09-05 13:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:11</t>
+          <t>更新时间: 2026-09-05 14:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 14:58</t>
+          <t>更新时间: 2026-09-05 16:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 16:01</t>
+          <t>更新时间: 2026-09-06 09:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 09:21</t>
+          <t>更新时间: 2026-09-06 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 12:36</t>
+          <t>更新时间: 2026-09-06 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:25</t>
+          <t>更新时间: 2026-09-06 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 15:10</t>
+          <t>更新时间: 2026-09-06 16:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 16:19</t>
+          <t>更新时间: 2026-09-07 09:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 09:22</t>
+          <t>更新时间: 2026-09-07 12:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 12:39</t>
+          <t>更新时间: 2026-09-07 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:35</t>
+          <t>更新时间: 2026-09-07 15:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 15:23</t>
+          <t>更新时间: 2026-09-07 16:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 16:52</t>
+          <t>更新时间: 2026-09-08 09:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 09:29</t>
+          <t>更新时间: 2026-09-08 12:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 12:33</t>
+          <t>更新时间: 2026-09-08 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:32</t>
+          <t>更新时间: 2026-09-08 15:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 15:18</t>
+          <t>更新时间: 2026-09-08 16:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 16:33</t>
+          <t>更新时间: 2026-09-09 09:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 09:34</t>
+          <t>更新时间: 2026-09-09 12:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 12:39</t>
+          <t>更新时间: 2026-09-09 13:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:39</t>
+          <t>更新时间: 2026-09-09 15:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 15:26</t>
+          <t>更新时间: 2026-09-09 16:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 16:34</t>
+          <t>更新时间: 2026-09-10 09:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 09:36</t>
+          <t>更新时间: 2026-09-10 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 12:40</t>
+          <t>更新时间: 2026-09-10 13:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:29</t>
+          <t>更新时间: 2026-09-10 15:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 15:22</t>
+          <t>更新时间: 2026-09-10 16:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 16:37</t>
+          <t>更新时间: 2026-09-11 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 09:32</t>
+          <t>更新时间: 2026-09-11 12:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 12:38</t>
+          <t>更新时间: 2026-09-11 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:32</t>
+          <t>更新时间: 2026-09-11 15:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 15:20</t>
+          <t>更新时间: 2026-09-11 16:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 16:31</t>
+          <t>更新时间: 2026-09-12 09:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 09:31</t>
+          <t>更新时间: 2026-09-12 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 12:32</t>
+          <t>更新时间: 2026-09-12 13:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:19</t>
+          <t>更新时间: 2026-09-12 15:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 15:13</t>
+          <t>更新时间: 2026-09-12 16:19</t>
         </is>
       </c>
     </row>
